--- a/gd/excel/complex_showcase.xlsx
+++ b/gd/excel/complex_showcase.xlsx
@@ -863,7 +863,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>示例主键，覆盖 64 位整数</t>
+          <t>示例主键（主键固定 int32；64 位整数覆盖见 SecretSeed 与 LongValues）</t>
         </is>
       </c>
       <c r="B1" s="2" t="inlineStr">
@@ -1021,7 +1021,7 @@
               <color rgb="FF8A5A00"/>
               <sz val="9"/>
             </rPr>
-            <t>int64</t>
+            <t>int32</t>
           </r>
         </is>
       </c>
@@ -1034,17 +1034,17 @@
               <color rgb="FF172033"/>
               <sz val="11"/>
             </rPr>
-            <t xml:space="preserve">Code
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-              <i val="1"/>
-              <color rgb="FF64748B"/>
-              <sz val="9"/>
-            </rPr>
-            <t>int32</t>
+            <t xml:space="preserve">CodeName
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <i val="1"/>
+              <color rgb="FF64748B"/>
+              <sz val="9"/>
+            </rPr>
+            <t>string</t>
           </r>
         </is>
       </c>
@@ -3250,8 +3250,10 @@
       <c r="A9" t="n">
         <v>1001</v>
       </c>
-      <c r="B9" t="n">
-        <v>101</v>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
       </c>
       <c r="C9" t="n">
         <v>1.25</v>
@@ -3465,8 +3467,10 @@
       <c r="A10" t="n">
         <v>1002</v>
       </c>
-      <c r="B10" t="n">
-        <v>202</v>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>202</t>
+        </is>
       </c>
       <c r="C10" t="n">
         <v>0.5</v>
@@ -3620,8 +3624,10 @@
       <c r="A11" t="n">
         <v>1003</v>
       </c>
-      <c r="B11" t="n">
-        <v>303</v>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>303</t>
+        </is>
       </c>
       <c r="C11" t="n">
         <v>9.75</v>
@@ -3750,8 +3756,10 @@
       <c r="A12" t="n">
         <v>1004</v>
       </c>
-      <c r="B12" t="n">
-        <v>304</v>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>304</t>
+        </is>
       </c>
       <c r="C12" t="n">
         <v>2</v>
@@ -4041,7 +4049,7 @@
     <mergeCell ref="AT1:BG1"/>
   </mergeCells>
   <dataValidations count="54">
-    <dataValidation sqref="B9:B1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="whole" operator="between">
+    <dataValidation sqref="A9:A1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="whole" operator="between">
       <formula1>-2147483648</formula1>
       <formula2>2147483647</formula2>
     </dataValidation>
